--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,52</t>
+          <t>-2,68; 1,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,2</t>
+          <t>-3,16; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -1,27</t>
+          <t>-5,42; -1,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,19</t>
+          <t>-2,35; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,42</t>
+          <t>-2,49; 1,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -1,84</t>
+          <t>-5,31; -1,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,79</t>
+          <t>-1,87; 0,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,61</t>
+          <t>-2,21; 0,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; -2,1</t>
+          <t>-4,71; -2,16</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 34,13</t>
+          <t>-37,92; 33,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 27,53</t>
+          <t>-45,46; 26,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,05; -22,7</t>
+          <t>-75,61; -19,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 24,15</t>
+          <t>-34,25; 26,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 29,38</t>
+          <t>-36,84; 27,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,4; -34,79</t>
+          <t>-74,88; -33,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 15,81</t>
+          <t>-28,44; 16,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 12,05</t>
+          <t>-33,04; 16,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,53; -40,07</t>
+          <t>-70,78; -39,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,46</t>
+          <t>-0,5; 2,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,19</t>
+          <t>-1,58; 1,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,91</t>
+          <t>-3,61; -0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,49</t>
+          <t>-0,86; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,95</t>
+          <t>-3,71; -0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -2,17</t>
+          <t>-5,14; -2,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,81</t>
+          <t>-0,31; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,23</t>
+          <t>-2,23; -0,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; -1,94</t>
+          <t>-3,84; -1,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 64,06</t>
+          <t>-10,15; 63,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 31,24</t>
+          <t>-31,15; 30,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,62; -23,74</t>
+          <t>-71,08; -24,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 44,08</t>
+          <t>-12,39; 44,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,37; -17,4</t>
+          <t>-51,48; -13,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,15; -37,43</t>
+          <t>-70,26; -37,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 37,41</t>
+          <t>-5,8; 41,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,51; -4,47</t>
+          <t>-37,09; 0,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -38,42</t>
+          <t>-64,74; -38,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -0,82</t>
+          <t>-4,83; -0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,34</t>
+          <t>-2,72; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,07</t>
+          <t>-3,66; 0,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,5</t>
+          <t>-2,68; 3,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,72</t>
+          <t>-2,79; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -1,09</t>
+          <t>-5,91; -1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,56</t>
+          <t>-2,86; 0,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,94</t>
+          <t>-1,63; 2,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,88</t>
+          <t>-4,05; -0,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,64; -27,67</t>
+          <t>-92,26; -22,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 103,33</t>
+          <t>-53,31; 84,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 10,31</t>
+          <t>-75,46; 25,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 99,06</t>
+          <t>-43,53; 91,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 77,24</t>
+          <t>-43,52; 80,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,71; -22,16</t>
+          <t>-83,57; -27,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 17,04</t>
+          <t>-54,56; 21,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 56,89</t>
+          <t>-32,44; 61,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -25,11</t>
+          <t>-75,23; -29,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,05</t>
+          <t>-1,08; 1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,58</t>
+          <t>-1,55; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -1,59</t>
+          <t>-3,6; -1,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,39</t>
+          <t>-0,96; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,32</t>
+          <t>-2,57; -0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -2,41</t>
+          <t>-4,67; -2,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,88</t>
+          <t>-0,67; 0,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,13</t>
+          <t>-1,65; -0,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -2,36</t>
+          <t>-3,86; -2,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 24,76</t>
+          <t>-20,49; 26,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 13,57</t>
+          <t>-28,56; 13,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,89; -36,15</t>
+          <t>-67,59; -34,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 26,58</t>
+          <t>-14,5; 25,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,53; -5,22</t>
+          <t>-38,12; -6,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,9; -44,69</t>
+          <t>-69,57; -44,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 17,56</t>
+          <t>-11,65; 17,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,18; -2,52</t>
+          <t>-28,57; -3,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,86; -46,08</t>
+          <t>-64,45; -46,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-3,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,63</t>
+          <t>-2,86; 1,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,26</t>
+          <t>-3,63; 1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; -1,14</t>
+          <t>-4,69; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,32</t>
+          <t>-2,28; 1,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,35</t>
+          <t>-2,51; 1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -1,84</t>
+          <t>-4,83; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,86</t>
+          <t>-2,13; 0,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,83</t>
+          <t>-2,2; 0,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -2,16</t>
+          <t>-4,35; -1,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-55,67%</t>
+          <t>-45,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-59,12%</t>
+          <t>-55,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,73%</t>
+          <t>-51,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 33,7</t>
+          <t>-40,0; 29,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 26,03</t>
+          <t>-50,06; 25,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,61; -19,5</t>
+          <t>-67,2; -11,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 26,72</t>
+          <t>-34,14; 27,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 27,99</t>
+          <t>-36,68; 28,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,88; -33,98</t>
+          <t>-71,54; -31,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 16,69</t>
+          <t>-31,19; 14,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 16,52</t>
+          <t>-33,14; 13,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,78; -39,71</t>
+          <t>-65,62; -33,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-2,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,41</t>
+          <t>-0,65; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,15</t>
+          <t>-1,52; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -0,94</t>
+          <t>-3,04; -0,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,53</t>
+          <t>-0,99; 2,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -0,74</t>
+          <t>-3,9; -0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -2,09</t>
+          <t>-4,16; -1,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,02</t>
+          <t>-0,36; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,01</t>
+          <t>-2,24; -0,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -1,84</t>
+          <t>-3,13; -1,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-49,62%</t>
+          <t>-38,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-56,73%</t>
+          <t>-41,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,6%</t>
+          <t>-40,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 63,45</t>
+          <t>-13,24; 61,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 30,23</t>
+          <t>-30,0; 33,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -24,14</t>
+          <t>-58,35; -9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 44,83</t>
+          <t>-13,71; 46,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,48; -13,4</t>
+          <t>-51,35; -12,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -37,28</t>
+          <t>-55,94; -19,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 41,46</t>
+          <t>-5,92; 45,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 0,62</t>
+          <t>-37,13; -0,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,74; -38,92</t>
+          <t>-52,55; -22,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -0,87</t>
+          <t>-4,77; -0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,11</t>
+          <t>-2,61; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,25</t>
+          <t>-3,7; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,2</t>
+          <t>-2,63; 3,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,78</t>
+          <t>-3,01; 2,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; -1,08</t>
+          <t>-5,0; -0,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,67</t>
+          <t>-2,9; 0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,04</t>
+          <t>-1,91; 1,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -0,98</t>
+          <t>-3,55; -0,38</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-49,58%</t>
+          <t>-39,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-63,47%</t>
+          <t>-48,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-57,1%</t>
+          <t>-43,78%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-92,26; -22,65</t>
+          <t>-92,25; -17,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,31; 84,29</t>
+          <t>-54,81; 82,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 25,53</t>
+          <t>-72,02; 40,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 91,93</t>
+          <t>-42,53; 89,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 80,75</t>
+          <t>-47,27; 72,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -27,77</t>
+          <t>-74,43; 0,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 21,37</t>
+          <t>-55,99; 19,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 61,37</t>
+          <t>-36,79; 50,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,23; -29,62</t>
+          <t>-65,06; -7,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-2,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-2,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,07</t>
+          <t>-1,09; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,57</t>
+          <t>-1,53; 0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -1,49</t>
+          <t>-3,11; -1,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,35</t>
+          <t>-0,93; 1,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,39</t>
+          <t>-2,52; -0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -2,49</t>
+          <t>-3,79; -1,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,86</t>
+          <t>-0,76; 0,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,19</t>
+          <t>-1,71; -0,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -2,41</t>
+          <t>-3,11; -1,66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-53,6%</t>
+          <t>-43,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-57,87%</t>
+          <t>-45,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-55,96%</t>
+          <t>-44,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 26,18</t>
+          <t>-20,47; 23,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 13,9</t>
+          <t>-27,9; 13,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,59; -34,66</t>
+          <t>-57,17; -25,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 25,3</t>
+          <t>-13,97; 28,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -6,79</t>
+          <t>-38,19; -5,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -44,41</t>
+          <t>-56,16; -31,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 17,75</t>
+          <t>-12,92; 17,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,57; -3,82</t>
+          <t>-29,14; -3,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,45; -46,1</t>
+          <t>-54,18; -34,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
